--- a/02_加值成品/生物/生物1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-1 生物的特徵與生命現象　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物1-1 生物的特徵與生命現象　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>生物與非生物差別在於？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>有無生命現象</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>生命</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>生物獲取能量的現象是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>營養</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>攝取</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>生物產生後代是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>有無生命現象</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>生殖</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>繁殖</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>生物對刺激的反應是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>感應</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>有無生命現象</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>反應</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>生物由什麼構成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>延續種族</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>代謝</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>細胞</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>基本單位</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>生物會不會生長？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>代謝</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>會</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>生長</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>含羞草被碰觸閉合是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>感應</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>刺激</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>生物需要什麼維持生命？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>生長</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>營養</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>細菌屬於生物嗎？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>延續種族</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>變色/遷徙</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>由細胞組成</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>生物體內化學反應的總稱是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>代謝</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>代謝</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-1 生物的特徵與生命現象　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物1-1 生物的特徵與生命現象　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>植物不太移動是生物嗎？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>適應</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>有生命現象</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>生物排除廢物的過程屬？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>有無生命現象</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>代謝</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>排泄</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>種子發芽長成植物是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>會</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>生長</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>生命現象</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>生物適應環境的例子？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>有無生命現象</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>代謝</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>細胞</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>變色/遷徙</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>結晶會變大是生命現象嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>非生物</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>呼吸作用的目的是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>有無生命現象</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>獲取能量</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>生物繁殖的意義是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>延續種族</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>變色/遷徙</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>後代</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>汽車會動是生物嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>營養</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>獲取能量</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>無生命現象</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>青蛙冬眠以度過寒冬屬哪種生命現象？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>感應</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>有無生命現象</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>生物死亡後還有生命現象嗎？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>生殖</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>沒有</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>變色/遷徙</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>停止</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物1-1 生物的特徵與生命現象　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物1-1 生物的特徵與生命現象　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>如何判斷一個物體是否為生物？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>偵測並回應環境趨吉避凶</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>檢視是否具備多項生命現象與細胞構造</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>具營養生長生殖感應等生命現象</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>提高存活與繁殖機會</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>判斷</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何植物雖不明顯移動仍是生物？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>無細胞結構需寄主才能繁殖</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>需能量會代謝生長生殖感應由細胞組成</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>營養呼吸提供能量支持生長生殖等</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>具營養生長生殖感應等生命現象</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>生命</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>病毒為何在生物界地位特殊？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>無細胞結構需寄主才能繁殖</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>具營養生長生殖感應等生命現象</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>偵測並回應環境趨吉避凶</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>提高存活與繁殖機會</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>特殊</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>生命現象間如何相互關聯？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>偵測並回應環境趨吉避凶</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>結晶是物理堆積無代謝生殖</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>營養呼吸提供能量支持生長生殖等</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>提高存活與繁殖機會</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>關聯</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>結晶長大與生物生長差別？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>檢視是否具備多項生命現象與細胞構造</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>無細胞結構需寄主才能繁殖</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>提高存活與繁殖機會</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>結晶是物理堆積無代謝生殖</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>適應環境對生物生存的重要性？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>有遺傳物質但需寄主才能繁殖</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>提高存活與繁殖機會</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>檢視是否具備多項生命現象與細胞構造</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>無細胞結構需寄主才能繁殖</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>感應與運動如何幫助生物生存？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>營養、生殖、感應等</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>偵測並回應環境趨吉避凶</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>檢視是否具備多項生命現象與細胞構造</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>有遺傳物質但需寄主才能繁殖</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>生存</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>由生命現象歸納生物的共同特徵？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>無細胞結構需寄主才能繁殖</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>需能量會代謝生長生殖感應由細胞組成</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>偵測並回應環境趨吉避凶</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>營養呼吸提供能量支持生長生殖等</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>歸納</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>列舉三項生物共有的生命現象？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>偵測並回應環境趨吉避凶</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>提高存活與繁殖機會</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>營養、生殖、感應等</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>具營養生長生殖感應等生命現象</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>列舉</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何病毒介於生物與非生物之間？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>檢視是否具備多項生命現象與細胞構造</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>有遺傳物質但需寄主才能繁殖</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>無細胞結構需寄主才能繁殖</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>偵測並回應環境趨吉避凶</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>特殊</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>生命</t>
+          <t>生命現象：只有生物才會呼吸、生長、繁殖，這些現象合稱生命現象，非生物沒有</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>攝取</t>
+          <t>攝取養分：生物要靠吃東西或行光合作用來獲得能量，這種現象叫做營養</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>繁殖</t>
+          <t>繁殖後代：生物產生下一代讓種族延續下去，這種現象叫做生殖</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>反應</t>
+          <t>刺激反應：生物感覺到外界變化並做出反應，這種現象叫做感應</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>基本單位</t>
+          <t>基本單位：所有生物體都是由細胞這個最小的構造單位組成的</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>生長</t>
+          <t>生長現象：生物會從小長大，體積和重量增加，這是生物共有的特徵</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>刺激</t>
+          <t>刺激反應：植物碰到外界的刺激後做出反應，這種對刺激產生回應的現象就叫做感應</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>營養</t>
+          <t>需要能量：生物要靠營養獲得能量，才能進行呼吸、生長等各種生命活動</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>由細胞組成</t>
+          <t>由細胞組成：細菌雖然構造簡單、只有一個細胞，但具備生命現象，是由細胞組成的生物</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>代謝</t>
+          <t>代謝：生物體內進行的所有化學反應（如分解養分、合成物質）合稱代謝</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>有生命現象</t>
+          <t>有生命現象：植物雖然不太會移動，但仍會生長、行光合作用、開花結果，所以是生物</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>排泄</t>
+          <t>排泄作用：生物把體內用不到的廢物排出體外，這個過程屬於代謝的一部分</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>生命現象</t>
+          <t>生命現象：種子發芽後不斷長大變成植物，這正是生物生長現象的表現</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>適應環境：像動物換毛變色或候鳥遷徙，都是生物為了在環境中生存所做的調整</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>非生物</t>
+          <t>非生物特徵：結晶變大只是物質一層層堆積，沒有呼吸生長等生命現象，所以不是</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>獲取能量：生物透過呼吸作用分解養分，釋放出維持生命活動所需的能量</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>後代</t>
+          <t>延續種族：生物產生後代，可以讓自己的種族一直延續下去不會消失</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>無生命現象</t>
+          <t>無生命現象：汽車雖然會動，但不會自己生長、繁殖或呼吸，所以不是生物</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>適應：青蛙靠冬眠降低身體活動、減少能量消耗來度過寒冬，這是生物因應環境變化的適應現象</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>停止</t>
+          <t>停止：生物死亡後不會呼吸、生長、繁殖，所有生命現象都會停止</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>判斷</t>
+          <t>綜合判斷：要看它是不是由細胞組成，並具備營養、呼吸、生長、生殖等多項生命現象</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>生命</t>
+          <t>生命現象齊全：植物雖然不太移動，但仍有營養、生長、生殖、感應等生命現象，所以是生物</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>特殊</t>
+          <t>特殊構造：病毒沒有細胞構造，必須寄生在其他生物體內才能繁殖，介於生物與非生物之間</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>關聯</t>
+          <t>互相配合：生物先靠營養和呼吸取得能量，再用這些能量進行生長、生殖等其他生命活動</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>本質不同：結晶只是物質分子一層層物理性堆積變大，不會代謝或生殖，跟生物生長完全不同</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>有利生存：生物能適應環境變化，就比較容易存活下來並繁殖後代，避免被淘汰</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>生存</t>
+          <t>趨吉避凶：生物靠感應察覺環境中的危險或食物，再用運動去躲避或靠近，幫助自己活下去</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>歸納</t>
+          <t>共同特徵：所有生物都需要能量、會進行代謝、生長、生殖與感應，並且由細胞組成身體</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>列舉</t>
+          <t>列舉：生物共有的生命現象包括攝取營養、行呼吸、生長發育、生殖繁衍、對刺激產生感應等，任舉三項即可</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>特殊</t>
+          <t>特殊：病毒具有遺傳物質，看似有生命，但自己無法獨立進行代謝與繁殖，必須靠寄生在寄主細胞內才能複製，所以性質介於生物和非生物之間</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物1-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物1-1_三種難度測驗卷.xlsx
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>細胞</t>
+          <t>感應</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>生長</t>
+          <t>沒有</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>沒有</t>
+          <t>生殖</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>延續種族</t>
+          <t>細胞</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>變色/遷徙</t>
+          <t>有無生命現象</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>感應</t>
+          <t>生殖</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>延續種族</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>生殖</t>
+          <t>感應</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>營養</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>細胞</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>感應</t>
+          <t>獲取能量</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>營養</t>
+          <t>有無生命現象</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>有無生命現象</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>營養</t>
+          <t>生長</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>感應</t>
+          <t>生殖</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>感應</t>
+          <t>會</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>營養</t>
+          <t>生殖</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>獲取能量</t>
+          <t>有無生命現象</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
